--- a/artfynd/A 24799-2026 artfynd.xlsx
+++ b/artfynd/A 24799-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134401399</v>
+        <v>137340450</v>
       </c>
       <c r="B3" t="n">
-        <v>8460</v>
+        <v>58189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,24 +833,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dåstorp, Dåstorp, Srm</t>
+          <t>Långängen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660345</v>
+        <v>660281</v>
       </c>
       <c r="R3" t="n">
-        <v>6557136</v>
+        <v>6557056</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,16 +891,245 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137340450</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137340141</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58756</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>660367</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6557076</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137340141</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134401399</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dåstorp, Dåstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>660345</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6557136</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134401399</t>
         </is>
@@ -923,6 +1139,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24799-2026 artfynd.xlsx
+++ b/artfynd/A 24799-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137340450</v>
       </c>
       <c r="B3" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137340141</v>
       </c>
       <c r="B4" t="n">
-        <v>58756</v>
+        <v>58758</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24799-2026 artfynd.xlsx
+++ b/artfynd/A 24799-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137340450</v>
       </c>
       <c r="B3" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137340141</v>
       </c>
       <c r="B4" t="n">
-        <v>58758</v>
+        <v>58760</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24799-2026 artfynd.xlsx
+++ b/artfynd/A 24799-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137340450</v>
       </c>
       <c r="B3" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137340141</v>
       </c>
       <c r="B4" t="n">
-        <v>58760</v>
+        <v>58763</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
